--- a/diseases/d058/2000-2004.xlsx
+++ b/diseases/d058/2000-2004.xlsx
@@ -773,6 +773,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -918,6 +923,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1063,6 +1073,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1208,6 +1223,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1353,6 +1373,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1498,6 +1523,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1643,6 +1673,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1788,6 +1823,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1933,6 +1973,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2078,6 +2123,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2223,6 +2273,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2368,6 +2423,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2513,6 +2573,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2658,6 +2723,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2803,6 +2873,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2948,6 +3023,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3093,6 +3173,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3238,6 +3323,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3383,6 +3473,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3528,6 +3623,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3673,6 +3773,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3818,6 +3923,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3963,6 +4073,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4108,6 +4223,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4253,6 +4373,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4401,6 +4526,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4546,6 +4676,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4694,6 +4829,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4839,6 +4979,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4987,6 +5132,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5132,6 +5282,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5280,6 +5435,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5425,6 +5585,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5573,6 +5738,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5718,6 +5888,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5866,6 +6041,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6011,6 +6191,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6159,6 +6344,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6304,6 +6494,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6452,6 +6647,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6597,6 +6797,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6745,6 +6950,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6890,6 +7100,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7038,6 +7253,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7183,6 +7403,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7331,6 +7556,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7476,6 +7706,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7624,6 +7859,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7769,6 +8009,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7917,6 +8162,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO51" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8062,6 +8312,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8210,6 +8465,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8355,6 +8615,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8503,6 +8768,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO55" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8648,6 +8918,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8796,6 +9071,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO57" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8941,6 +9221,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9089,6 +9374,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO59" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9234,6 +9524,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9382,6 +9677,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO61" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9527,6 +9827,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO62" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9675,6 +9980,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO63" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9820,6 +10130,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO64" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9968,6 +10283,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO65" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10113,6 +10433,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO66" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10261,6 +10586,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO67" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10406,6 +10736,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO68" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10554,6 +10889,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO69" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10699,6 +11039,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO70" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10847,6 +11192,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO71" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10992,6 +11342,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO72" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11138,6 +11493,11 @@
       <c r="S73" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">

--- a/diseases/d058/2000-2004.xlsx
+++ b/diseases/d058/2000-2004.xlsx
@@ -768,11 +768,6 @@
       <c r="R2" t="n">
         <v>0.01062846812229064</v>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -785,23 +780,13 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
         <v>0</v>
       </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV2" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -918,11 +903,6 @@
       <c r="R3" t="n">
         <v>0.002125693624458129</v>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -935,23 +915,13 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
       </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV3" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -1068,11 +1038,6 @@
       <c r="R4" t="n">
         <v>0.002125693624458129</v>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1085,23 +1050,13 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
         <v>0</v>
       </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV4" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -1218,11 +1173,6 @@
       <c r="R5" t="n">
         <v>0.002125693624458129</v>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1235,23 +1185,13 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
       </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV5" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -1368,11 +1308,6 @@
       <c r="R6" t="n">
         <v>0.002125693624458129</v>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1385,23 +1320,13 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0</v>
       </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV6" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -1518,11 +1443,6 @@
       <c r="R7" t="n">
         <v>0</v>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1535,23 +1455,13 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>0</v>
       </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV7" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -1668,11 +1578,6 @@
       <c r="R8" t="n">
         <v>0.008502774497832516</v>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1685,23 +1590,13 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
       </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV8" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -1818,11 +1713,6 @@
       <c r="R9" t="n">
         <v>0.008502774497832516</v>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1835,23 +1725,13 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
       </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV9" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -1968,11 +1848,6 @@
       <c r="R10" t="n">
         <v>0.0148798553712069</v>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1985,23 +1860,13 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
         <v>0</v>
       </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV10" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -2118,11 +1983,6 @@
       <c r="R11" t="n">
         <v>2.140573479829336</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2135,23 +1995,13 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
         <v>0</v>
       </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV11" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -2268,11 +2118,6 @@
       <c r="R12" t="n">
         <v>3.186414743062735</v>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2285,23 +2130,13 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
       </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV12" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -2418,11 +2253,6 @@
       <c r="R13" t="n">
         <v>0.2274492178170198</v>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2435,23 +2265,13 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
       </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV13" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -2568,11 +2388,6 @@
       <c r="R14" t="n">
         <v>0.0126852252992738</v>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2585,23 +2400,13 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
       </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV14" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -2718,11 +2523,6 @@
       <c r="R15" t="n">
         <v>0.006342612649636899</v>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2735,23 +2535,13 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
       </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV15" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -2868,11 +2658,6 @@
       <c r="R16" t="n">
         <v>0.006342612649636899</v>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2885,23 +2670,13 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
       </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV16" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -3018,11 +2793,6 @@
       <c r="R17" t="n">
         <v>0.002114204216545633</v>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3035,23 +2805,13 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
         <v>0</v>
       </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV17" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -3168,11 +2928,6 @@
       <c r="R18" t="n">
         <v>0.01479942951581943</v>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3185,23 +2940,13 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="n">
         <v>0</v>
       </c>
-      <c r="AU18" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV18" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -3318,11 +3063,6 @@
       <c r="R19" t="n">
         <v>0.01479942951581943</v>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3335,23 +3075,13 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
         <v>0</v>
       </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV19" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -3468,11 +3198,6 @@
       <c r="R20" t="n">
         <v>0.006342612649636899</v>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3485,23 +3210,13 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
         <v>0</v>
       </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV20" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -3618,11 +3333,6 @@
       <c r="R21" t="n">
         <v>0.01057102108272817</v>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3635,23 +3345,13 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
         <v>0</v>
       </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV21" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -3768,11 +3468,6 @@
       <c r="R22" t="n">
         <v>0.04651249276400393</v>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3785,23 +3480,13 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="n">
         <v>0</v>
       </c>
-      <c r="AU22" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV22" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -3918,11 +3603,6 @@
       <c r="R23" t="n">
         <v>2.033864456316899</v>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3935,23 +3615,13 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="n">
         <v>0</v>
       </c>
-      <c r="AU23" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV23" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -4068,11 +3738,6 @@
       <c r="R24" t="n">
         <v>1.782274154547969</v>
       </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4085,23 +3750,13 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR24" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="n">
         <v>0</v>
       </c>
-      <c r="AU24" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV24" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -4218,11 +3873,6 @@
       <c r="R25" t="n">
         <v>0.1205096403431011</v>
       </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4235,23 +3885,13 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR25" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="n">
         <v>0</v>
       </c>
-      <c r="AU25" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV25" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -4368,11 +4008,6 @@
       <c r="R26" t="n">
         <v>0.01052317866375857</v>
       </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4385,23 +4020,13 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR26" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="n">
         <v>0</v>
       </c>
-      <c r="AU26" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV26" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -4521,11 +4146,6 @@
       <c r="R27" t="n">
         <v>0.0352980764820631</v>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4538,23 +4158,13 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR27" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="n">
         <v>0</v>
       </c>
-      <c r="AU27" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV27" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
@@ -4671,11 +4281,6 @@
       <c r="R28" t="n">
         <v>0.006313907198255139</v>
       </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4688,23 +4293,13 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR28" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="n">
         <v>0</v>
       </c>
-      <c r="AU28" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV28" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -4824,11 +4419,6 @@
       <c r="R29" t="n">
         <v>0.02206129780128943</v>
       </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4841,23 +4431,13 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR29" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="n">
         <v>0</v>
       </c>
-      <c r="AU29" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV29" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
@@ -4974,11 +4554,6 @@
       <c r="R30" t="n">
         <v>0.004209271465503426</v>
       </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4991,23 +4566,13 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR30" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="n">
         <v>0</v>
       </c>
-      <c r="AU30" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV30" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -5127,11 +4692,6 @@
       <c r="R31" t="n">
         <v>0.008824519120515774</v>
       </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5144,23 +4704,13 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR31" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="n">
         <v>0</v>
       </c>
-      <c r="AU31" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV31" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
@@ -5277,11 +4827,6 @@
       <c r="R32" t="n">
         <v>0.008418542931006853</v>
       </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5294,23 +4839,13 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR32" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="n">
         <v>0</v>
       </c>
-      <c r="AU32" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV32" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -5430,11 +4965,6 @@
       <c r="R33" t="n">
         <v>0.05294711472309464</v>
       </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5447,23 +4977,13 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR33" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="n">
         <v>0</v>
       </c>
-      <c r="AU33" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV33" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
@@ -5580,11 +5100,6 @@
       <c r="R34" t="n">
         <v>0.01473245012926199</v>
       </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5597,23 +5112,13 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR34" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="n">
         <v>0</v>
       </c>
-      <c r="AU34" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV34" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -5733,11 +5238,6 @@
       <c r="R35" t="n">
         <v>0.1014819698859314</v>
       </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5750,23 +5250,13 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR35" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="n">
         <v>0</v>
       </c>
-      <c r="AU35" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV35" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
@@ -5883,11 +5373,6 @@
       <c r="R36" t="n">
         <v>0.01262781439651028</v>
       </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5900,23 +5385,13 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR36" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="n">
         <v>0</v>
       </c>
-      <c r="AU36" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV36" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -6036,11 +5511,6 @@
       <c r="R37" t="n">
         <v>0.1676658632897997</v>
       </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6053,23 +5523,13 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR37" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="n">
         <v>0</v>
       </c>
-      <c r="AU37" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV37" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
@@ -6186,11 +5646,6 @@
       <c r="R38" t="n">
         <v>0.006313907198255139</v>
       </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6203,23 +5658,13 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR38" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="n">
         <v>0</v>
       </c>
-      <c r="AU38" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV38" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -6339,11 +5784,6 @@
       <c r="R39" t="n">
         <v>0.3176826883385679</v>
       </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6356,23 +5796,13 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR39" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="n">
         <v>0</v>
       </c>
-      <c r="AU39" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV39" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
@@ -6489,11 +5919,6 @@
       <c r="R40" t="n">
         <v>0.002104635732751713</v>
       </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6506,23 +5931,13 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR40" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="n">
         <v>0</v>
       </c>
-      <c r="AU40" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV40" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -6642,11 +6057,6 @@
       <c r="R41" t="n">
         <v>0.1058942294461893</v>
       </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6659,23 +6069,13 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR41" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="n">
         <v>0</v>
       </c>
-      <c r="AU41" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV41" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
@@ -6792,11 +6192,6 @@
       <c r="R42" t="n">
         <v>0.01894172159476542</v>
       </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6809,23 +6204,13 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR42" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="n">
         <v>0</v>
       </c>
-      <c r="AU42" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV42" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -6945,11 +6330,6 @@
       <c r="R43" t="n">
         <v>0.1235432676872208</v>
       </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6962,23 +6342,13 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR43" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="n">
         <v>0</v>
       </c>
-      <c r="AU43" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV43" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
@@ -7095,11 +6465,6 @@
       <c r="R44" t="n">
         <v>1.3511761404266</v>
       </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7112,23 +6477,13 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR44" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="n">
         <v>0</v>
       </c>
-      <c r="AU44" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV44" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -7248,11 +6603,6 @@
       <c r="R45" t="n">
         <v>0.1720781228500576</v>
       </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7265,23 +6615,13 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR45" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="n">
         <v>0</v>
       </c>
-      <c r="AU45" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV45" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
@@ -7398,11 +6738,6 @@
       <c r="R46" t="n">
         <v>1.3511761404266</v>
       </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7415,23 +6750,13 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR46" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="n">
         <v>0</v>
       </c>
-      <c r="AU46" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV46" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -7551,11 +6876,6 @@
       <c r="R47" t="n">
         <v>0.1323677868077366</v>
       </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7568,23 +6888,13 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR47" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="n">
         <v>0</v>
       </c>
-      <c r="AU47" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV47" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
@@ -7701,11 +7011,6 @@
       <c r="R48" t="n">
         <v>0.1915218516804059</v>
       </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7718,23 +7023,13 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR48" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="n">
         <v>0</v>
       </c>
-      <c r="AU48" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV48" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -7854,11 +7149,6 @@
       <c r="R49" t="n">
         <v>0.06618389340386829</v>
       </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7871,23 +7161,13 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR49" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="n">
         <v>0</v>
       </c>
-      <c r="AU49" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV49" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
@@ -8004,11 +7284,6 @@
       <c r="R50" t="n">
         <v>0.01467595219753043</v>
       </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8021,23 +7296,13 @@
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR50" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="n">
         <v>0</v>
       </c>
-      <c r="AU50" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV50" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -8157,11 +7422,6 @@
       <c r="R51" t="n">
         <v>0.05715433574329719</v>
       </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8174,23 +7434,13 @@
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR51" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="n">
         <v>0</v>
       </c>
-      <c r="AU51" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV51" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
@@ -8307,11 +7557,6 @@
       <c r="R52" t="n">
         <v>0.002096564599647205</v>
       </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8324,23 +7569,13 @@
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR52" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="n">
         <v>0</v>
       </c>
-      <c r="AU52" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV52" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -8460,11 +7695,6 @@
       <c r="R53" t="n">
         <v>0.02637892418921409</v>
       </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8477,23 +7707,13 @@
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR53" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="n">
         <v>0</v>
       </c>
-      <c r="AU53" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV53" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
@@ -8610,11 +7830,6 @@
       <c r="R54" t="n">
         <v>0.004193129199294409</v>
       </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8627,23 +7842,13 @@
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR54" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="n">
         <v>0</v>
       </c>
-      <c r="AU54" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV54" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -8763,11 +7968,6 @@
       <c r="R55" t="n">
         <v>0.008792974729738031</v>
       </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8780,23 +7980,13 @@
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR55" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="n">
         <v>0</v>
       </c>
-      <c r="AU55" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV55" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
@@ -8913,11 +8103,6 @@
       <c r="R56" t="n">
         <v>0.004193129199294409</v>
       </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8930,23 +8115,13 @@
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR56" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="n">
         <v>0</v>
       </c>
-      <c r="AU56" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV56" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -9066,11 +8241,6 @@
       <c r="R57" t="n">
         <v>0.04836136101355916</v>
       </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9083,23 +8253,13 @@
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR57" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="n">
         <v>0</v>
       </c>
-      <c r="AU57" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV57" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
@@ -9216,11 +8376,6 @@
       <c r="R58" t="n">
         <v>0.01257938759788323</v>
       </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9233,23 +8388,13 @@
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR58" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="n">
         <v>0</v>
       </c>
-      <c r="AU58" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV58" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -9369,11 +8514,6 @@
       <c r="R59" t="n">
         <v>0.1362911083109395</v>
       </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9386,23 +8526,13 @@
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR59" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="n">
         <v>0</v>
       </c>
-      <c r="AU59" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV59" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
@@ -9519,11 +8649,6 @@
       <c r="R60" t="n">
         <v>0.01257938759788323</v>
       </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9536,23 +8661,13 @@
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR60" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS60" t="inlineStr"/>
       <c r="AT60" t="n">
         <v>0</v>
       </c>
-      <c r="AU60" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV60" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -9672,11 +8787,6 @@
       <c r="R61" t="n">
         <v>0.2374103177029268</v>
       </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9689,23 +8799,13 @@
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR61" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS61" t="inlineStr"/>
       <c r="AT61" t="n">
         <v>0</v>
       </c>
-      <c r="AU61" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV61" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
@@ -9822,11 +8922,6 @@
       <c r="R62" t="n">
         <v>0</v>
       </c>
-      <c r="S62" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9839,23 +8934,13 @@
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR62" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS62" t="inlineStr"/>
       <c r="AT62" t="n">
         <v>0</v>
       </c>
-      <c r="AU62" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV62" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -9975,11 +9060,6 @@
       <c r="R63" t="n">
         <v>0.2549962671624029</v>
       </c>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9992,23 +9072,13 @@
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR63" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="n">
         <v>0</v>
       </c>
-      <c r="AU63" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV63" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
@@ -10125,11 +9195,6 @@
       <c r="R64" t="n">
         <v>0.01257938759788323</v>
       </c>
-      <c r="S64" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10142,23 +9207,13 @@
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR64" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS64" t="inlineStr"/>
       <c r="AT64" t="n">
         <v>0</v>
       </c>
-      <c r="AU64" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV64" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -10278,11 +9333,6 @@
       <c r="R65" t="n">
         <v>0.3165470902705691</v>
       </c>
-      <c r="S65" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10295,23 +9345,13 @@
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR65" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="n">
         <v>0</v>
       </c>
-      <c r="AU65" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV65" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
@@ -10428,11 +9468,6 @@
       <c r="R66" t="n">
         <v>0.02935190439506087</v>
       </c>
-      <c r="S66" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10445,23 +9480,13 @@
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR66" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS66" t="inlineStr"/>
       <c r="AT66" t="n">
         <v>0</v>
       </c>
-      <c r="AU66" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV66" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -10581,11 +9606,6 @@
       <c r="R67" t="n">
         <v>0.3253400650003071</v>
       </c>
-      <c r="S67" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10598,23 +9618,13 @@
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR67" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS67" t="inlineStr"/>
       <c r="AT67" t="n">
         <v>0</v>
       </c>
-      <c r="AU67" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV67" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
@@ -10731,11 +9741,6 @@
       <c r="R68" t="n">
         <v>3.834616652754737</v>
       </c>
-      <c r="S68" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10748,23 +9753,13 @@
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR68" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS68" t="inlineStr"/>
       <c r="AT68" t="n">
         <v>0</v>
       </c>
-      <c r="AU68" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV68" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -10884,11 +9879,6 @@
       <c r="R69" t="n">
         <v>0.1318946209460704</v>
       </c>
-      <c r="S69" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10901,23 +9891,13 @@
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR69" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="n">
         <v>0</v>
       </c>
-      <c r="AU69" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV69" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
@@ -11034,11 +10014,6 @@
       <c r="R70" t="n">
         <v>5.591537787259095</v>
       </c>
-      <c r="S70" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11051,23 +10026,13 @@
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR70" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS70" t="inlineStr"/>
       <c r="AT70" t="n">
         <v>0</v>
       </c>
-      <c r="AU70" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV70" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -11187,11 +10152,6 @@
       <c r="R71" t="n">
         <v>0.1318946209460704</v>
       </c>
-      <c r="S71" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11204,23 +10164,13 @@
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR71" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS71" t="inlineStr"/>
       <c r="AT71" t="n">
         <v>0</v>
       </c>
-      <c r="AU71" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV71" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
@@ -11337,11 +10287,6 @@
       <c r="R72" t="n">
         <v>0.3312572067442583</v>
       </c>
-      <c r="S72" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11354,23 +10299,13 @@
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR72" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS72" t="inlineStr"/>
       <c r="AT72" t="n">
         <v>0</v>
       </c>
-      <c r="AU72" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV72" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -11490,11 +10425,6 @@
       <c r="R73" t="n">
         <v>0.07913677256764227</v>
       </c>
-      <c r="S73" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11507,22 +10437,12 @@
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR73" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS73" t="inlineStr"/>
       <c r="AT73" t="n">
         <v>0</v>
-      </c>
-      <c r="AU73" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV73" t="inlineStr">
         <is>

--- a/diseases/d058/2000-2004.xlsx
+++ b/diseases/d058/2000-2004.xlsx
@@ -768,6 +768,11 @@
       <c r="R2" t="n">
         <v>0.01062846812229064</v>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -780,13 +785,23 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
         <v>0</v>
       </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV2" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -903,6 +918,11 @@
       <c r="R3" t="n">
         <v>0.002125693624458129</v>
       </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -915,13 +935,23 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
       </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV3" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -1038,6 +1068,11 @@
       <c r="R4" t="n">
         <v>0.002125693624458129</v>
       </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1050,13 +1085,23 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
         <v>0</v>
       </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV4" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -1173,6 +1218,11 @@
       <c r="R5" t="n">
         <v>0.002125693624458129</v>
       </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1185,13 +1235,23 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
       </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV5" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -1308,6 +1368,11 @@
       <c r="R6" t="n">
         <v>0.002125693624458129</v>
       </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1320,13 +1385,23 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0</v>
       </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV6" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -1443,6 +1518,11 @@
       <c r="R7" t="n">
         <v>0</v>
       </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1455,13 +1535,23 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>0</v>
       </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV7" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -1578,6 +1668,11 @@
       <c r="R8" t="n">
         <v>0.008502774497832516</v>
       </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1590,13 +1685,23 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
       </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV8" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -1713,6 +1818,11 @@
       <c r="R9" t="n">
         <v>0.008502774497832516</v>
       </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1725,13 +1835,23 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
       </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV9" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -1848,6 +1968,11 @@
       <c r="R10" t="n">
         <v>0.0148798553712069</v>
       </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1860,13 +1985,23 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
         <v>0</v>
       </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV10" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -1983,6 +2118,11 @@
       <c r="R11" t="n">
         <v>2.140573479829336</v>
       </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1995,13 +2135,23 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
         <v>0</v>
       </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV11" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -2118,6 +2268,11 @@
       <c r="R12" t="n">
         <v>3.186414743062735</v>
       </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2130,13 +2285,23 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
       </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV12" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -2253,6 +2418,11 @@
       <c r="R13" t="n">
         <v>0.2274492178170198</v>
       </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2265,13 +2435,23 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
       </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV13" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -2388,6 +2568,11 @@
       <c r="R14" t="n">
         <v>0.0126852252992738</v>
       </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2400,13 +2585,23 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
       </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV14" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -2523,6 +2718,11 @@
       <c r="R15" t="n">
         <v>0.006342612649636899</v>
       </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2535,13 +2735,23 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
       </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV15" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -2658,6 +2868,11 @@
       <c r="R16" t="n">
         <v>0.006342612649636899</v>
       </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2670,13 +2885,23 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
       </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV16" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -2793,6 +3018,11 @@
       <c r="R17" t="n">
         <v>0.002114204216545633</v>
       </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2805,13 +3035,23 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
         <v>0</v>
       </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV17" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -2928,6 +3168,11 @@
       <c r="R18" t="n">
         <v>0.01479942951581943</v>
       </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2940,13 +3185,23 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="n">
         <v>0</v>
       </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV18" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -3063,6 +3318,11 @@
       <c r="R19" t="n">
         <v>0.01479942951581943</v>
       </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3075,13 +3335,23 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
         <v>0</v>
       </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV19" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -3198,6 +3468,11 @@
       <c r="R20" t="n">
         <v>0.006342612649636899</v>
       </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3210,13 +3485,23 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
         <v>0</v>
       </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV20" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -3333,6 +3618,11 @@
       <c r="R21" t="n">
         <v>0.01057102108272817</v>
       </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3345,13 +3635,23 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
         <v>0</v>
       </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV21" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -3468,6 +3768,11 @@
       <c r="R22" t="n">
         <v>0.04651249276400393</v>
       </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3480,13 +3785,23 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="n">
         <v>0</v>
       </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV22" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -3603,6 +3918,11 @@
       <c r="R23" t="n">
         <v>2.033864456316899</v>
       </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3615,13 +3935,23 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="n">
         <v>0</v>
       </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV23" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -3738,6 +4068,11 @@
       <c r="R24" t="n">
         <v>1.782274154547969</v>
       </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3750,13 +4085,23 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="n">
         <v>0</v>
       </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV24" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -3873,6 +4218,11 @@
       <c r="R25" t="n">
         <v>0.1205096403431011</v>
       </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3885,13 +4235,23 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="n">
         <v>0</v>
       </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV25" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -4008,6 +4368,11 @@
       <c r="R26" t="n">
         <v>0.01052317866375857</v>
       </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4020,13 +4385,23 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="n">
         <v>0</v>
       </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV26" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -4281,6 +4656,11 @@
       <c r="R28" t="n">
         <v>0.006313907198255139</v>
       </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4293,13 +4673,23 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="n">
         <v>0</v>
       </c>
+      <c r="AU28" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV28" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -4554,6 +4944,11 @@
       <c r="R30" t="n">
         <v>0.004209271465503426</v>
       </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4566,13 +4961,23 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR30" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="n">
         <v>0</v>
       </c>
+      <c r="AU30" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV30" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -4827,6 +5232,11 @@
       <c r="R32" t="n">
         <v>0.008418542931006853</v>
       </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4839,13 +5249,23 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR32" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="n">
         <v>0</v>
       </c>
+      <c r="AU32" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV32" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -5100,6 +5520,11 @@
       <c r="R34" t="n">
         <v>0.01473245012926199</v>
       </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5112,13 +5537,23 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR34" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="n">
         <v>0</v>
       </c>
+      <c r="AU34" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV34" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -5373,6 +5808,11 @@
       <c r="R36" t="n">
         <v>0.01262781439651028</v>
       </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5385,13 +5825,23 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR36" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="n">
         <v>0</v>
       </c>
+      <c r="AU36" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV36" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -5646,6 +6096,11 @@
       <c r="R38" t="n">
         <v>0.006313907198255139</v>
       </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5658,13 +6113,23 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR38" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="n">
         <v>0</v>
       </c>
+      <c r="AU38" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV38" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -5919,6 +6384,11 @@
       <c r="R40" t="n">
         <v>0.002104635732751713</v>
       </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5931,13 +6401,23 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR40" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="n">
         <v>0</v>
       </c>
+      <c r="AU40" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV40" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -6192,6 +6672,11 @@
       <c r="R42" t="n">
         <v>0.01894172159476542</v>
       </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6204,13 +6689,23 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR42" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="n">
         <v>0</v>
       </c>
+      <c r="AU42" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV42" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -6465,6 +6960,11 @@
       <c r="R44" t="n">
         <v>1.3511761404266</v>
       </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6477,13 +6977,23 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR44" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="n">
         <v>0</v>
       </c>
+      <c r="AU44" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV44" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -6738,6 +7248,11 @@
       <c r="R46" t="n">
         <v>1.3511761404266</v>
       </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6750,13 +7265,23 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR46" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="n">
         <v>0</v>
       </c>
+      <c r="AU46" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV46" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -7011,6 +7536,11 @@
       <c r="R48" t="n">
         <v>0.1915218516804059</v>
       </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7023,13 +7553,23 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR48" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="n">
         <v>0</v>
       </c>
+      <c r="AU48" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV48" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -7284,6 +7824,11 @@
       <c r="R50" t="n">
         <v>0.01467595219753043</v>
       </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7296,13 +7841,23 @@
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR50" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="n">
         <v>0</v>
       </c>
+      <c r="AU50" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV50" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -7557,6 +8112,11 @@
       <c r="R52" t="n">
         <v>0.002096564599647205</v>
       </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7569,13 +8129,23 @@
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR52" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="n">
         <v>0</v>
       </c>
+      <c r="AU52" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV52" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -7830,6 +8400,11 @@
       <c r="R54" t="n">
         <v>0.004193129199294409</v>
       </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7842,13 +8417,23 @@
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR54" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="n">
         <v>0</v>
       </c>
+      <c r="AU54" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV54" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -8103,6 +8688,11 @@
       <c r="R56" t="n">
         <v>0.004193129199294409</v>
       </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8115,13 +8705,23 @@
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR56" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="n">
         <v>0</v>
       </c>
+      <c r="AU56" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV56" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -8376,6 +8976,11 @@
       <c r="R58" t="n">
         <v>0.01257938759788323</v>
       </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8388,13 +8993,23 @@
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR58" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="n">
         <v>0</v>
       </c>
+      <c r="AU58" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV58" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -8649,6 +9264,11 @@
       <c r="R60" t="n">
         <v>0.01257938759788323</v>
       </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8661,13 +9281,23 @@
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR60" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS60" t="inlineStr"/>
       <c r="AT60" t="n">
         <v>0</v>
       </c>
+      <c r="AU60" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV60" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -8922,6 +9552,11 @@
       <c r="R62" t="n">
         <v>0</v>
       </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8934,13 +9569,23 @@
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR62" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS62" t="inlineStr"/>
       <c r="AT62" t="n">
         <v>0</v>
       </c>
+      <c r="AU62" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV62" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -9195,6 +9840,11 @@
       <c r="R64" t="n">
         <v>0.01257938759788323</v>
       </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9207,13 +9857,23 @@
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR64" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS64" t="inlineStr"/>
       <c r="AT64" t="n">
         <v>0</v>
       </c>
+      <c r="AU64" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV64" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -9468,6 +10128,11 @@
       <c r="R66" t="n">
         <v>0.02935190439506087</v>
       </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9480,13 +10145,23 @@
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR66" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS66" t="inlineStr"/>
       <c r="AT66" t="n">
         <v>0</v>
       </c>
+      <c r="AU66" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV66" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -9741,6 +10416,11 @@
       <c r="R68" t="n">
         <v>3.834616652754737</v>
       </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9753,13 +10433,23 @@
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR68" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS68" t="inlineStr"/>
       <c r="AT68" t="n">
         <v>0</v>
       </c>
+      <c r="AU68" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV68" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -10014,6 +10704,11 @@
       <c r="R70" t="n">
         <v>5.591537787259095</v>
       </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10026,13 +10721,23 @@
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR70" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS70" t="inlineStr"/>
       <c r="AT70" t="n">
         <v>0</v>
       </c>
+      <c r="AU70" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV70" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -10287,6 +10992,11 @@
       <c r="R72" t="n">
         <v>0.3312572067442583</v>
       </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10299,12 +11009,22 @@
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR72" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS72" t="inlineStr"/>
       <c r="AT72" t="n">
         <v>0</v>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV72" t="inlineStr">
         <is>
